--- a/Machine/Machines.xlsx
+++ b/Machine/Machines.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AI\ProdPlan\Machine\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9296F6E-354A-4DDE-8B71-F6AE04734FC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D282B98E-C061-4A37-96C6-F6C509EE68E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Furnace 1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="22">
   <si>
     <t>Name</t>
   </si>
@@ -456,7 +456,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AM21"/>
+  <dimension ref="A1:AK21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.21875" bestFit="1" customWidth="1"/>
@@ -519,7 +519,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="20" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>12</v>
       </c>
@@ -537,7 +537,7 @@
         <v>3</v>
       </c>
       <c r="F20">
-        <f t="shared" ref="F20:AL20" si="0">E20+1</f>
+        <f t="shared" ref="F20:AJ20" si="0">E20+1</f>
         <v>4</v>
       </c>
       <c r="G20">
@@ -660,16 +660,8 @@
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="AK20">
-        <f t="shared" si="0"/>
-        <v>35</v>
-      </c>
-      <c r="AL20">
-        <f t="shared" si="0"/>
-        <v>36</v>
-      </c>
-    </row>
-    <row r="21" spans="1:39" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>13</v>
       </c>
@@ -744,10 +736,10 @@
       <c r="X21">
         <v>1000</v>
       </c>
-      <c r="AL21">
-        <v>200</v>
-      </c>
-      <c r="AM21" t="s">
+      <c r="AJ21">
+        <v>300</v>
+      </c>
+      <c r="AK21" t="s">
         <v>11</v>
       </c>
     </row>
@@ -758,7 +750,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36BE85E0-FB0B-42C3-B38A-F5ED44818443}">
-  <dimension ref="A1:AM21"/>
+  <dimension ref="A1:AK21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.21875" bestFit="1" customWidth="1"/>
@@ -821,7 +813,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="20" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>12</v>
       </c>
@@ -962,16 +954,8 @@
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="AK20">
-        <f t="shared" si="0"/>
-        <v>35</v>
-      </c>
-      <c r="AL20">
-        <f t="shared" si="0"/>
-        <v>36</v>
-      </c>
-    </row>
-    <row r="21" spans="1:39" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>13</v>
       </c>
@@ -1046,10 +1030,10 @@
       <c r="X21">
         <v>1000</v>
       </c>
-      <c r="AL21">
-        <v>200</v>
-      </c>
-      <c r="AM21" t="s">
+      <c r="AJ21">
+        <v>300</v>
+      </c>
+      <c r="AK21" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1124,6 +1108,9 @@
       </c>
     </row>
     <row r="20" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>12</v>
+      </c>
       <c r="B20">
         <v>0</v>
       </c>
@@ -1740,7 +1727,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6835B0CD-A8C8-4A7B-A7E9-86AAA5AF77E1}">
-  <dimension ref="A1:AM21"/>
+  <dimension ref="A1:AK21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.21875" bestFit="1" customWidth="1"/>
@@ -1803,7 +1790,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="20" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>12</v>
       </c>
@@ -1944,16 +1931,8 @@
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="AK20">
-        <f t="shared" si="0"/>
-        <v>35</v>
-      </c>
-      <c r="AL20">
-        <f t="shared" si="0"/>
-        <v>36</v>
-      </c>
-    </row>
-    <row r="21" spans="1:39" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>13</v>
       </c>
@@ -2028,10 +2007,10 @@
       <c r="X21">
         <v>1000</v>
       </c>
-      <c r="AL21">
-        <v>200</v>
-      </c>
-      <c r="AM21" t="s">
+      <c r="AJ21">
+        <v>300</v>
+      </c>
+      <c r="AK21" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2042,7 +2021,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC81CA44-2003-42C0-87B1-6F07DAD63A52}">
-  <dimension ref="A1:AM21"/>
+  <dimension ref="A1:AK21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.21875" bestFit="1" customWidth="1"/>
@@ -2105,7 +2084,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="20" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>12</v>
       </c>
@@ -2246,16 +2225,8 @@
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="AK20">
-        <f t="shared" si="0"/>
-        <v>35</v>
-      </c>
-      <c r="AL20">
-        <f t="shared" si="0"/>
-        <v>36</v>
-      </c>
-    </row>
-    <row r="21" spans="1:39" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>13</v>
       </c>
@@ -2330,10 +2301,10 @@
       <c r="X21">
         <v>1000</v>
       </c>
-      <c r="AL21">
-        <v>200</v>
-      </c>
-      <c r="AM21" t="s">
+      <c r="AJ21">
+        <v>300</v>
+      </c>
+      <c r="AK21" t="s">
         <v>11</v>
       </c>
     </row>

--- a/Machine/Machines.xlsx
+++ b/Machine/Machines.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AI\ProdPlan\Machine\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D282B98E-C061-4A37-96C6-F6C509EE68E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C080A64-B0BF-48BA-99AC-4F9A19D87F88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Furnace 1" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="Furnace 4" sheetId="5" r:id="rId4"/>
     <sheet name="Furnace 5" sheetId="4" r:id="rId5"/>
     <sheet name="Furnace 6" sheetId="6" r:id="rId6"/>
+    <sheet name="Rules" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="26">
   <si>
     <t>Name</t>
   </si>
@@ -130,6 +131,18 @@
   </si>
   <si>
     <t>Furnace 6</t>
+  </si>
+  <si>
+    <t>Furnace 1 and Furnace 2 cannot heat at the same time</t>
+  </si>
+  <si>
+    <t>Furnace 5 and Furnace 6 cannot heat at the same time</t>
+  </si>
+  <si>
+    <t>It takes one hour to load a furnace before heating</t>
+  </si>
+  <si>
+    <t>It takes one hour to unload a furnace after cooling</t>
   </si>
 </sst>
 </file>
@@ -831,7 +844,7 @@
         <v>3</v>
       </c>
       <c r="F20">
-        <f t="shared" ref="F20:AL20" si="0">E20+1</f>
+        <f t="shared" ref="F20:AJ20" si="0">E20+1</f>
         <v>4</v>
       </c>
       <c r="G20">
@@ -1808,7 +1821,7 @@
         <v>3</v>
       </c>
       <c r="F20">
-        <f t="shared" ref="F20:AL20" si="0">E20+1</f>
+        <f t="shared" ref="F20:AJ20" si="0">E20+1</f>
         <v>4</v>
       </c>
       <c r="G20">
@@ -2102,7 +2115,7 @@
         <v>3</v>
       </c>
       <c r="F20">
-        <f t="shared" ref="F20:AL20" si="0">E20+1</f>
+        <f t="shared" ref="F20:AJ20" si="0">E20+1</f>
         <v>4</v>
       </c>
       <c r="G20">
@@ -2306,6 +2319,39 @@
       </c>
       <c r="AK21" t="s">
         <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E86D9E1E-DE9C-42B3-ACE9-0D3B54436532}">
+  <dimension ref="A2:A5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/Machine/Machines.xlsx
+++ b/Machine/Machines.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AI\ProdPlan\Machine\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C080A64-B0BF-48BA-99AC-4F9A19D87F88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D7C2F4F-3470-4D83-89CE-2FBEE30F36D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="30">
   <si>
     <t>Name</t>
   </si>
@@ -143,6 +143,18 @@
   </si>
   <si>
     <t>It takes one hour to unload a furnace after cooling</t>
+  </si>
+  <si>
+    <t>Furnace 1 and Furnace 3 cannot heat at the same time</t>
+  </si>
+  <si>
+    <t>Furnace 2 and Furnace 3 cannot heat at the same time</t>
+  </si>
+  <si>
+    <t>Furnace 4 and Furnace 6 cannot heat at the same time</t>
+  </si>
+  <si>
+    <t>Furnace 4 and Furnace 5 cannot heat at the same time</t>
   </si>
 </sst>
 </file>
@@ -2328,7 +2340,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E86D9E1E-DE9C-42B3-ACE9-0D3B54436532}">
-  <dimension ref="A2:A5"/>
+  <dimension ref="A2:A9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
@@ -2341,16 +2353,36 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>25</v>
       </c>
     </row>

--- a/Machine/Machines.xlsx
+++ b/Machine/Machines.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AI\ProdPlan\Machine\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D7C2F4F-3470-4D83-89CE-2FBEE30F36D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F15A1276-BE65-4A53-AA0D-EB5DD3C2BB92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,6 +20,7 @@
     <sheet name="Furnace 5" sheetId="4" r:id="rId5"/>
     <sheet name="Furnace 6" sheetId="6" r:id="rId6"/>
     <sheet name="Rules" sheetId="7" r:id="rId7"/>
+    <sheet name="Electricity" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="50">
   <si>
     <t>Name</t>
   </si>
@@ -156,12 +157,72 @@
   <si>
     <t>Furnace 4 and Furnace 5 cannot heat at the same time</t>
   </si>
+  <si>
+    <t>Coating line</t>
+  </si>
+  <si>
+    <t>Vacuum system 02</t>
+  </si>
+  <si>
+    <t>Furnace 7</t>
+  </si>
+  <si>
+    <t>Cooling system 1</t>
+  </si>
+  <si>
+    <t>Cooling system 2</t>
+  </si>
+  <si>
+    <t>Pre treatment</t>
+  </si>
+  <si>
+    <t>R&amp;D</t>
+  </si>
+  <si>
+    <t>Facility</t>
+  </si>
+  <si>
+    <t>Cooling system 1 need to run during both heating and cooling for furnace 1, furnace 2 and furnace 3</t>
+  </si>
+  <si>
+    <t>Cooling system 2 needs to run during both heating and cooling for furnace 4, furnace 5 and furnace 6</t>
+  </si>
+  <si>
+    <t>Vacuum system 01</t>
+  </si>
+  <si>
+    <t>Vacuum system 01 needs to run during both heating and cooling for furnace 3</t>
+  </si>
+  <si>
+    <t>Vacuum system 02 needs to run during both heating and cooling for furnace 4</t>
+  </si>
+  <si>
+    <t>Unknown</t>
+  </si>
+  <si>
+    <t>Run coating line as much as possible</t>
+  </si>
+  <si>
+    <t>Coating line needs 200A electricity during first 2 hours, then 100A for continuous running. If it stops, then it has to heat up again with 200A for 2 hours</t>
+  </si>
+  <si>
+    <t>Pre-treatment (45 A) and Furnace 7 (82 A) are Editable inputs, default off</t>
+  </si>
+  <si>
+    <t>Coating line has high priority, try not to break it</t>
+  </si>
+  <si>
+    <t>Furnaces use electricity during during heating process</t>
+  </si>
+  <si>
+    <t>Treat furnace 4, 5, and 6 as ampere 0. They use seperate power resource</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -177,16 +238,34 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -194,13 +273,58 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2340,10 +2464,10 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E86D9E1E-DE9C-42B3-ACE9-0D3B54436532}">
-  <dimension ref="A2:A9"/>
+  <dimension ref="A2:A19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="124.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
@@ -2384,6 +2508,184 @@
     <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>49</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D7714B5-87FF-4AFD-A6BE-2928C5B4828C}">
+  <dimension ref="A1:B15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.88671875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="6">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="7">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="7">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="7">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="7">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="7">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="8"/>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="8"/>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="8"/>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" s="7">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" s="7">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="7">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="7">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
